--- a/output/2026-09-01_20_Italia_Marche_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-01_20_Italia_Marche_Depolverazione_Trattamento_aria.xlsx
@@ -558,7 +558,6 @@
           <t>Giuliodori Roberto S.r.l.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Macerata (Appignano) - Marche</t>
@@ -574,7 +573,6 @@
           <t>0733 400050</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Azienda reale confermata (P.IVA 01364670438, fax 0733 400310) tramite PagineBianche/PagineGialle. Nessun sito web ne email pubblica reperibile.</t>
@@ -612,10 +610,9 @@
           <t>0721 499043</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Telefono corretto confermato da fonti indipendenti (elenchitelefonici.it, paginegialle.it); 0721 808968 riportato dal ricercatore era un errore di directory (appartiene a Centroventilazione). Email non reperita.</t>
+          <t>Telefono corretto confermato da fonti indipendenti (elenchitelefonici.it, paginegialle.it); 0721 808968 riportato dal ricercatore era un errore di directory (appartiene a Centroventilazione). Email non reperita. [DUPLICATO — vedi anche: 2026-09-01_19_Italia_Marche_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -657,7 +654,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Verificata pienamente (P.IVA 00173870411), attiva dal 1974.</t>
+          <t>Verificata pienamente (P.IVA 00173870411), attiva dal 1974. [DUPLICATO — vedi anche: 2026-09-01_19_Italia_Marche_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -692,10 +689,9 @@
           <t>0721 498517</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Azienda confermata. Secondo numero riportato dal ricercatore (0721 476657) non riscontrato da fonti indipendenti. Email guerra@baruccaimpianti.it NON confermata (dominio di terzi) - lasciata vuota.</t>
+          <t>Azienda confermata. Secondo numero riportato dal ricercatore (0721 476657) non riscontrato da fonti indipendenti. Email guerra@baruccaimpianti.it NON confermata (dominio di terzi) - lasciata vuota. [DUPLICATO — vedi anche: 2026-09-01_19_Italia_Marche_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -737,7 +733,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Verificata. Distributore confermato Parker/Kaeser/Leybold (non Beko come riportato inizialmente dal ricercatore - correzione).</t>
+          <t>Verificata. Distributore confermato Parker/Kaeser/Leybold (non Beko come riportato inizialmente dal ricercatore - correzione). [DUPLICATO — vedi anche: 2026-09-01_19_Italia_Marche_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -856,7 +852,6 @@
           <t>0734 674799 / 0734 673645</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Verificata (P.IVA 01762720447), attiva dal 1978. Email non reperita.</t>
